--- a/artfynd/A 25394-2026 artfynd.xlsx
+++ b/artfynd/A 25394-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137452234</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137452237</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
